--- a/src/assets/templates/template_repasse_ipva.xlsx
+++ b/src/assets/templates/template_repasse_ipva.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcos Andre\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcos Andre\Pictures\CRIPTO - DEPLOY ADM VERCEL\frontend-administrador\src\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114D2591-4942-4274-917A-72104E157575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0666BB40-A564-4C24-85E2-1CC14C5A5750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3036" yWindow="3036" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>Resultado Consulta Repasse dos Municípios</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>TOTAIS</t>
+  </si>
+  <si>
+    <t>IPVA</t>
   </si>
 </sst>
 </file>
@@ -362,6 +365,63 @@
     <xf numFmtId="4" fontId="3" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -375,63 +435,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -718,80 +721,82 @@
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="20"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="15"/>
     </row>
     <row r="2" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="25"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="20"/>
     </row>
     <row r="3" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="29"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="24"/>
     </row>
     <row r="4" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="32"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="27"/>
     </row>
     <row r="5" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="16"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="11"/>
     </row>
     <row r="6" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="18"/>
+      <c r="B6" s="13"/>
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
@@ -818,8 +823,8 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10"/>
+      <c r="A7" s="28"/>
+      <c r="B7" s="29"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -830,10 +835,10 @@
       <c r="J7" s="5"/>
     </row>
     <row r="8" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="12"/>
+      <c r="B8" s="31"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -845,6 +850,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="A6:B6"/>
@@ -858,11 +868,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
